--- a/公立三级_二级医院名单.xlsx
+++ b/公立三级_二级医院名单.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="3264" windowHeight="22340"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>序号</t>
   </si>
@@ -68,7 +68,13 @@
     <t>东城区</t>
   </si>
   <si>
-    <t>北京市东城区第一人民医院</t>
+    <t>北京医院</t>
+  </si>
+  <si>
+    <t>北京中医药大学东直门医院</t>
+  </si>
+  <si>
+    <t>首都医科大学附属北京妇产医院</t>
   </si>
 </sst>
 </file>
@@ -1020,14 +1026,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="9.2" customWidth="1"/>
+    <col min="1" max="1" width="9.19642857142857" customWidth="1"/>
     <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="11.5416666666667" customWidth="1"/>
-    <col min="5" max="5" width="38.65" customWidth="1"/>
-    <col min="6" max="8" width="13.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5446428571429" customWidth="1"/>
+    <col min="5" max="5" width="38.6517857142857" customWidth="1"/>
+    <col min="6" max="8" width="13.3303571428571" style="1" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1065,7 +1071,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1079,12 +1085,46 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J2" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J4" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/公立三级_二级医院名单.xlsx
+++ b/公立三级_二级医院名单.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="3264" windowHeight="22340"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$9347</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="57">
   <si>
     <t>序号</t>
   </si>
@@ -47,6 +47,18 @@
     <t>医院名称</t>
   </si>
   <si>
+    <t>省卫健委网址</t>
+  </si>
+  <si>
+    <t>市卫健委网址</t>
+  </si>
+  <si>
+    <t>区卫健委网址</t>
+  </si>
+  <si>
+    <t>医院官网</t>
+  </si>
+  <si>
     <t>2024年决算-总收入</t>
   </si>
   <si>
@@ -68,6 +80,27 @@
     <t>东城区</t>
   </si>
   <si>
+    <t>北京市东城区第一人民医院</t>
+  </si>
+  <si>
+    <t>2024决算: https://www.bjdch.gov.cn/ztzl/bmyjsgkzl/bmjsgkzl/2024njs/qzf2024js/202507/t20250725_4158528.html; 2025预算: https://www.bjdch.gov.cn/ztzl/bmyjsgkzl/bmysgkzl/2025nys/qzf2025ys/202502/t20250217_4013018.html; 2026预算: https://www.bjdch.gov.cn/ztzl/bmyjsgkzl/bmysgkzl/2026nys/qzf2026ys/202602/t20260212_4510811.html</t>
+  </si>
+  <si>
+    <t>单位均为万元。2024决算数精确值为30739.037847万元，来自收入支出决算总表本年收入合计决算数列；2025和2026来自预算01表部门单位收支总表本年收入合计预算数列。</t>
+  </si>
+  <si>
+    <t>北京市鼓楼中医医院</t>
+  </si>
+  <si>
+    <t>三年数据均来源于北京市东城区政府网站东城区部门预决算公开专栏，单位为万元；2024为决算数（本年收入合计），2025和2026为预算数（本年收入合计）</t>
+  </si>
+  <si>
+    <t>北京市和平里医院</t>
+  </si>
+  <si>
+    <t>金额单位：万元；数据来源为北京市东城区部门预决算公开专栏；2024决算数取自收入支出决算总表本年收入合计决算数；2025、2026预算数取自部门单位收支总表本年收入合计预算数</t>
+  </si>
+  <si>
     <t>北京医院</t>
   </si>
   <si>
@@ -75,6 +108,99 @@
   </si>
   <si>
     <t>首都医科大学附属北京妇产医院</t>
+  </si>
+  <si>
+    <t>首都医科大学附属北京中医医院</t>
+  </si>
+  <si>
+    <t>中国医学科学院北京协和医院</t>
+  </si>
+  <si>
+    <t>北京市第六医院</t>
+  </si>
+  <si>
+    <t>北京市隆福医院</t>
+  </si>
+  <si>
+    <t>北京市普仁医院</t>
+  </si>
+  <si>
+    <t>首都医科大学附属北京口腔医院</t>
+  </si>
+  <si>
+    <t>首都医科大学附属北京同仁医院</t>
+  </si>
+  <si>
+    <t>西城区</t>
+  </si>
+  <si>
+    <t>北京按摩医院</t>
+  </si>
+  <si>
+    <t>北京市宣武中医医院</t>
+  </si>
+  <si>
+    <t>通州区</t>
+  </si>
+  <si>
+    <t>首都医科大学附属北京友谊医院</t>
+  </si>
+  <si>
+    <t>首都医科大学附属复兴医院</t>
+  </si>
+  <si>
+    <t>中国医学科学院阜外医院</t>
+  </si>
+  <si>
+    <t>北京市监狱管理局清河分局医院</t>
+  </si>
+  <si>
+    <t>北京市西城区展览路医院</t>
+  </si>
+  <si>
+    <t>首都医科大学宣武医院</t>
+  </si>
+  <si>
+    <t>首都医科大学附属北京安定医院</t>
+  </si>
+  <si>
+    <t>北京市监狱管理局中心医院</t>
+  </si>
+  <si>
+    <t>昌平区</t>
+  </si>
+  <si>
+    <t>北京积水潭医院</t>
+  </si>
+  <si>
+    <t>北京中医药大学附属护国寺中医医院</t>
+  </si>
+  <si>
+    <t>首都医科大学附属北京儿童医院</t>
+  </si>
+  <si>
+    <t>北京大学第一医院</t>
+  </si>
+  <si>
+    <t>北京大学人民医院</t>
+  </si>
+  <si>
+    <t>北京市西城区平安医院</t>
+  </si>
+  <si>
+    <t>北京市第二医院</t>
+  </si>
+  <si>
+    <t>北京市肛肠医院</t>
+  </si>
+  <si>
+    <t>北京市西城区广外医院</t>
+  </si>
+  <si>
+    <t>中国中医科学院广安门医院</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -557,148 +683,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1026,18 +1152,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <dimension ref="A1:N9318"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.19642857142857" customWidth="1"/>
+    <col min="1" max="1" width="9.2" customWidth="1"/>
     <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="11.5446428571429" customWidth="1"/>
-    <col min="5" max="5" width="38.6517857142857" customWidth="1"/>
-    <col min="6" max="8" width="13.3303571428571" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="4" max="4" width="11.5416666666667" customWidth="1"/>
+    <col min="5" max="5" width="38.65" customWidth="1"/>
+    <col min="6" max="8" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="8.875" customWidth="1"/>
+    <col min="10" max="12" width="13.3333333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6666666666667" customWidth="1"/>
+    <col min="14" max="14" width="11.325" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1053,78 +1182,656 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2">
+        <v>30739.04</v>
+      </c>
+      <c r="K2">
+        <v>34054.18</v>
+      </c>
+      <c r="L2">
+        <v>31387.23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3">
+        <v>41629.03</v>
+      </c>
+      <c r="K3">
+        <v>42311.81</v>
+      </c>
+      <c r="L3">
+        <v>37734.16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4">
+        <v>70965.05</v>
+      </c>
+      <c r="K4">
+        <v>75444.87</v>
+      </c>
+      <c r="L4">
+        <v>74402.89</v>
+      </c>
+      <c r="M4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4">
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>63</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>71</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>76</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9318" spans="10:10">
+      <c r="J9318" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N9347" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
